--- a/GameDesign/Excel/Drop.xlsx
+++ b/GameDesign/Excel/Drop.xlsx
@@ -7,6 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="FishingBasicTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FarmingBasicTable" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LoggingBasicTable" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MiningBasicTable" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="HuntingBasicTable" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -667,86 +671,5026 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
+        <v>101</v>
+      </c>
+      <c r="C10" t="n">
         <v>10001</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1001</v>
       </c>
       <c r="D10" t="n">
         <v>6590</v>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>0.659</v>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>붕어</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
+        <v>102</v>
+      </c>
+      <c r="C11" t="n">
         <v>10002</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1002</v>
       </c>
       <c r="D11" t="n">
         <v>2000</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>0.2</v>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>잉어</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
+        <v>103</v>
+      </c>
+      <c r="C12" t="n">
         <v>10003</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1003</v>
       </c>
       <c r="D12" t="n">
         <v>1000</v>
       </c>
-      <c r="E12" s="10" t="n">
-        <v>0.1</v>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>월척 붕어</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
+        <v>104</v>
+      </c>
+      <c r="C13" t="n">
         <v>10004</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1004</v>
       </c>
       <c r="D13" t="n">
         <v>300</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>0.03</v>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>향어</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
+        <v>105</v>
+      </c>
+      <c r="C14" t="n">
         <v>10005</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1005</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>0.01</v>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>대물 잉어</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
+        <v>106</v>
+      </c>
+      <c r="C15" t="n">
         <v>10006</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1006</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>0.001</v>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>전설의 잉어</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="E20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="E27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="E34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="E35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="E36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="E37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="E38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="E39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="E40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="E41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="E42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="E43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="E44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="E45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="E46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="E47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="E48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="E49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="E50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="E51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="E55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="E56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="E57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="E58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="E59" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="E60" s="10" t="n"/>
+    </row>
+    <row r="61">
+      <c r="E61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="E62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="E63" s="10" t="n"/>
+    </row>
+    <row r="64">
+      <c r="E64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="E65" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="E66" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="E67" s="10" t="n"/>
+    </row>
+    <row r="68">
+      <c r="E68" s="10" t="n"/>
+    </row>
+    <row r="69">
+      <c r="E69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="E70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="E71" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="E72" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="E73" s="10" t="n"/>
+    </row>
+    <row r="74">
+      <c r="E74" s="10" t="n"/>
+    </row>
+    <row r="75">
+      <c r="E75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="E76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="E77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="E78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="E79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="E80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="E81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="E82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="E83" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="E84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="E85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="E87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="E88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="E89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="E90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="E91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="E92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="E93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="E94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="E95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="E96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="E97" s="10" t="n"/>
+    </row>
+    <row r="98">
+      <c r="E98" s="10" t="n"/>
+    </row>
+    <row r="99">
+      <c r="E99" s="10" t="n"/>
+    </row>
+    <row r="100">
+      <c r="E100" s="10" t="n"/>
+    </row>
+    <row r="101">
+      <c r="E101" s="10" t="n"/>
+    </row>
+    <row r="102">
+      <c r="E102" s="10" t="n"/>
+    </row>
+    <row r="103">
+      <c r="E103" s="10" t="n"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="10" t="n"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="10" t="n"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="10" t="n"/>
+    </row>
+    <row r="107">
+      <c r="E107" s="10" t="n"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="10" t="n"/>
+    </row>
+    <row r="109">
+      <c r="E109" s="10" t="n"/>
+    </row>
+    <row r="110">
+      <c r="E110" s="10" t="n"/>
+    </row>
+    <row r="111">
+      <c r="E111" s="10" t="n"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="10" t="n"/>
+    </row>
+    <row r="113">
+      <c r="E113" s="10" t="n"/>
+    </row>
+    <row r="114">
+      <c r="E114" s="10" t="n"/>
+    </row>
+    <row r="115">
+      <c r="E115" s="10" t="n"/>
+    </row>
+    <row r="116">
+      <c r="E116" s="10" t="n"/>
+    </row>
+    <row r="117">
+      <c r="E117" s="10" t="n"/>
+    </row>
+    <row r="118">
+      <c r="E118" s="10" t="n"/>
+    </row>
+    <row r="119">
+      <c r="E119" s="10" t="n"/>
+    </row>
+    <row r="120">
+      <c r="E120" s="10" t="n"/>
+    </row>
+    <row r="121">
+      <c r="E121" s="10" t="n"/>
+    </row>
+    <row r="122">
+      <c r="E122" s="10" t="n"/>
+    </row>
+    <row r="123">
+      <c r="E123" s="10" t="n"/>
+    </row>
+    <row r="124">
+      <c r="E124" s="10" t="n"/>
+    </row>
+    <row r="125">
+      <c r="E125" s="10" t="n"/>
+    </row>
+    <row r="126">
+      <c r="E126" s="10" t="n"/>
+    </row>
+    <row r="127">
+      <c r="E127" s="10" t="n"/>
+    </row>
+    <row r="128">
+      <c r="E128" s="10" t="n"/>
+    </row>
+    <row r="129">
+      <c r="E129" s="10" t="n"/>
+    </row>
+    <row r="130">
+      <c r="E130" s="10" t="n"/>
+    </row>
+    <row r="131">
+      <c r="E131" s="10" t="n"/>
+    </row>
+    <row r="132">
+      <c r="E132" s="10" t="n"/>
+    </row>
+    <row r="133">
+      <c r="E133" s="10" t="n"/>
+    </row>
+    <row r="134">
+      <c r="E134" s="10" t="n"/>
+    </row>
+    <row r="135">
+      <c r="E135" s="10" t="n"/>
+    </row>
+    <row r="136">
+      <c r="E136" s="10" t="n"/>
+    </row>
+    <row r="137">
+      <c r="E137" s="10" t="n"/>
+    </row>
+    <row r="138">
+      <c r="E138" s="10" t="n"/>
+    </row>
+    <row r="139">
+      <c r="E139" s="10" t="n"/>
+    </row>
+    <row r="140">
+      <c r="E140" s="10" t="n"/>
+    </row>
+    <row r="141">
+      <c r="E141" s="10" t="n"/>
+    </row>
+    <row r="142">
+      <c r="E142" s="10" t="n"/>
+    </row>
+    <row r="143">
+      <c r="E143" s="10" t="n"/>
+    </row>
+    <row r="144">
+      <c r="E144" s="10" t="n"/>
+    </row>
+    <row r="145">
+      <c r="E145" s="10" t="n"/>
+    </row>
+    <row r="146">
+      <c r="E146" s="10" t="n"/>
+    </row>
+    <row r="147">
+      <c r="E147" s="10" t="n"/>
+    </row>
+    <row r="148">
+      <c r="E148" s="10" t="n"/>
+    </row>
+    <row r="149">
+      <c r="E149" s="10" t="n"/>
+    </row>
+    <row r="150">
+      <c r="E150" s="10" t="n"/>
+    </row>
+    <row r="151">
+      <c r="E151" s="10" t="n"/>
+    </row>
+    <row r="152">
+      <c r="E152" s="10" t="n"/>
+    </row>
+    <row r="153">
+      <c r="E153" s="10" t="n"/>
+    </row>
+    <row r="154">
+      <c r="E154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="E155" s="10" t="n"/>
+    </row>
+    <row r="156">
+      <c r="E156" s="10" t="n"/>
+    </row>
+    <row r="157">
+      <c r="E157" s="10" t="n"/>
+    </row>
+    <row r="158">
+      <c r="E158" s="10" t="n"/>
+    </row>
+    <row r="159">
+      <c r="E159" s="10" t="n"/>
+    </row>
+    <row r="160">
+      <c r="E160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="E161" s="10" t="n"/>
+    </row>
+    <row r="162">
+      <c r="E162" s="10" t="n"/>
+    </row>
+    <row r="163">
+      <c r="E163" s="10" t="n"/>
+    </row>
+    <row r="164">
+      <c r="E164" s="10" t="n"/>
+    </row>
+    <row r="165">
+      <c r="E165" s="10" t="n"/>
+    </row>
+    <row r="166">
+      <c r="E166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="E167" s="10" t="n"/>
+    </row>
+    <row r="168">
+      <c r="E168" s="10" t="n"/>
+    </row>
+    <row r="169">
+      <c r="E169" s="10" t="n"/>
+    </row>
+    <row r="170">
+      <c r="E170" s="10" t="n"/>
+    </row>
+    <row r="171">
+      <c r="E171" s="10" t="n"/>
+    </row>
+    <row r="172">
+      <c r="E172" s="10" t="n"/>
+    </row>
+    <row r="173">
+      <c r="E173" s="10" t="n"/>
+    </row>
+    <row r="174">
+      <c r="E174" s="10" t="n"/>
+    </row>
+    <row r="175">
+      <c r="E175" s="10" t="n"/>
+    </row>
+    <row r="176">
+      <c r="E176" s="10" t="n"/>
+    </row>
+    <row r="177">
+      <c r="E177" s="10" t="n"/>
+    </row>
+    <row r="178">
+      <c r="E178" s="10" t="n"/>
+    </row>
+    <row r="179">
+      <c r="E179" s="10" t="n"/>
+    </row>
+    <row r="180">
+      <c r="E180" s="10" t="n"/>
+    </row>
+    <row r="181">
+      <c r="E181" s="10" t="n"/>
+    </row>
+    <row r="182">
+      <c r="E182" s="10" t="n"/>
+    </row>
+    <row r="183">
+      <c r="E183" s="10" t="n"/>
+    </row>
+    <row r="184">
+      <c r="E184" s="10" t="n"/>
+    </row>
+    <row r="185">
+      <c r="E185" s="10" t="n"/>
+    </row>
+    <row r="186">
+      <c r="E186" s="10" t="n"/>
+    </row>
+    <row r="187">
+      <c r="E187" s="10" t="n"/>
+    </row>
+    <row r="188">
+      <c r="E188" s="10" t="n"/>
+    </row>
+    <row r="189">
+      <c r="E189" s="10" t="n"/>
+    </row>
+    <row r="190">
+      <c r="E190" s="10" t="n"/>
+    </row>
+    <row r="191">
+      <c r="E191" s="10" t="n"/>
+    </row>
+    <row r="192">
+      <c r="E192" s="10" t="n"/>
+    </row>
+    <row r="193">
+      <c r="E193" s="10" t="n"/>
+    </row>
+    <row r="194">
+      <c r="E194" s="10" t="n"/>
+    </row>
+    <row r="195">
+      <c r="E195" s="10" t="n"/>
+    </row>
+    <row r="196">
+      <c r="E196" s="10" t="n"/>
+    </row>
+    <row r="197">
+      <c r="E197" s="10" t="n"/>
+    </row>
+    <row r="198">
+      <c r="E198" s="10" t="n"/>
+    </row>
+    <row r="199">
+      <c r="E199" s="10" t="n"/>
+    </row>
+    <row r="200">
+      <c r="E200" s="10" t="n"/>
+    </row>
+    <row r="201">
+      <c r="E201" s="10" t="n"/>
+    </row>
+    <row r="202">
+      <c r="E202" s="10" t="n"/>
+    </row>
+    <row r="203">
+      <c r="E203" s="10" t="n"/>
+    </row>
+    <row r="204">
+      <c r="E204" s="10" t="n"/>
+    </row>
+    <row r="205">
+      <c r="E205" s="10" t="n"/>
+    </row>
+    <row r="206">
+      <c r="E206" s="10" t="n"/>
+    </row>
+    <row r="207">
+      <c r="E207" s="10" t="n"/>
+    </row>
+    <row r="208">
+      <c r="E208" s="10" t="n"/>
+    </row>
+    <row r="209">
+      <c r="E209" s="10" t="n"/>
+    </row>
+    <row r="210">
+      <c r="E210" s="10" t="n"/>
+    </row>
+    <row r="211">
+      <c r="E211" s="10" t="n"/>
+    </row>
+    <row r="212">
+      <c r="E212" s="10" t="n"/>
+    </row>
+    <row r="213">
+      <c r="E213" s="10" t="n"/>
+    </row>
+    <row r="214">
+      <c r="E214" s="10" t="n"/>
+    </row>
+    <row r="215">
+      <c r="E215" s="10" t="n"/>
+    </row>
+    <row r="216">
+      <c r="E216" s="10" t="n"/>
+    </row>
+    <row r="217">
+      <c r="E217" s="10" t="n"/>
+    </row>
+    <row r="218">
+      <c r="E218" s="10" t="n"/>
+    </row>
+    <row r="219">
+      <c r="E219" s="10" t="n"/>
+    </row>
+    <row r="220">
+      <c r="E220" s="10" t="n"/>
+    </row>
+    <row r="221">
+      <c r="E221" s="10" t="n"/>
+    </row>
+    <row r="222">
+      <c r="E222" s="10" t="n"/>
+    </row>
+    <row r="223">
+      <c r="E223" s="10" t="n"/>
+    </row>
+    <row r="224">
+      <c r="E224" s="10" t="n"/>
+    </row>
+    <row r="225">
+      <c r="E225" s="10" t="n"/>
+    </row>
+    <row r="226">
+      <c r="E226" s="10" t="n"/>
+    </row>
+    <row r="227">
+      <c r="E227" s="10" t="n"/>
+    </row>
+    <row r="228">
+      <c r="E228" s="10" t="n"/>
+    </row>
+    <row r="229">
+      <c r="E229" s="10" t="n"/>
+    </row>
+    <row r="230">
+      <c r="E230" s="10" t="n"/>
+    </row>
+    <row r="231">
+      <c r="E231" s="10" t="n"/>
+    </row>
+    <row r="232">
+      <c r="E232" s="10" t="n"/>
+    </row>
+    <row r="233">
+      <c r="E233" s="10" t="n"/>
+    </row>
+    <row r="234">
+      <c r="E234" s="10" t="n"/>
+    </row>
+    <row r="235">
+      <c r="E235" s="10" t="n"/>
+    </row>
+    <row r="236">
+      <c r="E236" s="10" t="n"/>
+    </row>
+    <row r="237">
+      <c r="E237" s="10" t="n"/>
+    </row>
+    <row r="238">
+      <c r="E238" s="10" t="n"/>
+    </row>
+    <row r="239">
+      <c r="E239" s="10" t="n"/>
+    </row>
+    <row r="240">
+      <c r="E240" s="10" t="n"/>
+    </row>
+    <row r="241">
+      <c r="E241" s="10" t="n"/>
+    </row>
+    <row r="242">
+      <c r="E242" s="10" t="n"/>
+    </row>
+    <row r="243">
+      <c r="E243" s="10" t="n"/>
+    </row>
+    <row r="244">
+      <c r="E244" s="10" t="n"/>
+    </row>
+    <row r="245">
+      <c r="E245" s="10" t="n"/>
+    </row>
+    <row r="246">
+      <c r="E246" s="10" t="n"/>
+    </row>
+    <row r="247">
+      <c r="E247" s="10" t="n"/>
+    </row>
+    <row r="248">
+      <c r="E248" s="10" t="n"/>
+    </row>
+    <row r="249">
+      <c r="E249" s="10" t="n"/>
+    </row>
+    <row r="250">
+      <c r="E250" s="10" t="n"/>
+    </row>
+    <row r="251">
+      <c r="E251" s="10" t="n"/>
+    </row>
+    <row r="252">
+      <c r="E252" s="10" t="n"/>
+    </row>
+    <row r="253">
+      <c r="E253" s="10" t="n"/>
+    </row>
+    <row r="254">
+      <c r="E254" s="10" t="n"/>
+    </row>
+    <row r="255">
+      <c r="E255" s="10" t="n"/>
+    </row>
+    <row r="256">
+      <c r="E256" s="10" t="n"/>
+    </row>
+    <row r="257">
+      <c r="E257" s="10" t="n"/>
+    </row>
+    <row r="258">
+      <c r="E258" s="10" t="n"/>
+    </row>
+    <row r="259">
+      <c r="E259" s="10" t="n"/>
+    </row>
+    <row r="260">
+      <c r="E260" s="10" t="n"/>
+    </row>
+    <row r="261">
+      <c r="E261" s="10" t="n"/>
+    </row>
+    <row r="262">
+      <c r="E262" s="10" t="n"/>
+    </row>
+    <row r="263">
+      <c r="E263" s="10" t="n"/>
+    </row>
+    <row r="264">
+      <c r="E264" s="10" t="n"/>
+    </row>
+    <row r="265">
+      <c r="E265" s="10" t="n"/>
+    </row>
+    <row r="266">
+      <c r="E266" s="10" t="n"/>
+    </row>
+    <row r="267">
+      <c r="E267" s="10" t="n"/>
+    </row>
+    <row r="268">
+      <c r="E268" s="10" t="n"/>
+    </row>
+    <row r="269">
+      <c r="E269" s="10" t="n"/>
+    </row>
+    <row r="270">
+      <c r="E270" s="10" t="n"/>
+    </row>
+    <row r="271">
+      <c r="E271" s="10" t="n"/>
+    </row>
+    <row r="272">
+      <c r="E272" s="10" t="n"/>
+    </row>
+    <row r="273">
+      <c r="E273" s="10" t="n"/>
+    </row>
+    <row r="274">
+      <c r="E274" s="10" t="n"/>
+    </row>
+    <row r="275">
+      <c r="E275" s="10" t="n"/>
+    </row>
+    <row r="276">
+      <c r="E276" s="10" t="n"/>
+    </row>
+    <row r="277">
+      <c r="E277" s="10" t="n"/>
+    </row>
+    <row r="278">
+      <c r="E278" s="10" t="n"/>
+    </row>
+    <row r="279">
+      <c r="E279" s="10" t="n"/>
+    </row>
+    <row r="280">
+      <c r="E280" s="10" t="n"/>
+    </row>
+    <row r="281">
+      <c r="E281" s="10" t="n"/>
+    </row>
+    <row r="282">
+      <c r="E282" s="10" t="n"/>
+    </row>
+    <row r="283">
+      <c r="E283" s="10" t="n"/>
+    </row>
+    <row r="284">
+      <c r="E284" s="10" t="n"/>
+    </row>
+    <row r="285">
+      <c r="E285" s="10" t="n"/>
+    </row>
+    <row r="286">
+      <c r="E286" s="10" t="n"/>
+    </row>
+    <row r="287">
+      <c r="E287" s="10" t="n"/>
+    </row>
+    <row r="288">
+      <c r="E288" s="10" t="n"/>
+    </row>
+    <row r="289">
+      <c r="E289" s="10" t="n"/>
+    </row>
+    <row r="290">
+      <c r="E290" s="10" t="n"/>
+    </row>
+    <row r="291">
+      <c r="E291" s="10" t="n"/>
+    </row>
+    <row r="292">
+      <c r="E292" s="10" t="n"/>
+    </row>
+    <row r="293">
+      <c r="E293" s="10" t="n"/>
+    </row>
+    <row r="294">
+      <c r="E294" s="10" t="n"/>
+    </row>
+    <row r="295">
+      <c r="E295" s="10" t="n"/>
+    </row>
+    <row r="296">
+      <c r="E296" s="10" t="n"/>
+    </row>
+    <row r="297">
+      <c r="E297" s="10" t="n"/>
+    </row>
+    <row r="298">
+      <c r="E298" s="10" t="n"/>
+    </row>
+    <row r="299">
+      <c r="E299" s="10" t="n"/>
+    </row>
+    <row r="300">
+      <c r="E300" s="10" t="n"/>
+    </row>
+    <row r="301">
+      <c r="E301" s="10" t="n"/>
+    </row>
+    <row r="302">
+      <c r="E302" s="10" t="n"/>
+    </row>
+    <row r="303">
+      <c r="E303" s="10" t="n"/>
+    </row>
+    <row r="304">
+      <c r="E304" s="10" t="n"/>
+    </row>
+    <row r="305">
+      <c r="E305" s="10" t="n"/>
+    </row>
+    <row r="306">
+      <c r="E306" s="10" t="n"/>
+    </row>
+    <row r="307">
+      <c r="E307" s="10" t="n"/>
+    </row>
+    <row r="308">
+      <c r="E308" s="10" t="n"/>
+    </row>
+    <row r="309">
+      <c r="E309" s="10" t="n"/>
+    </row>
+    <row r="310">
+      <c r="E310" s="10" t="n"/>
+    </row>
+    <row r="311">
+      <c r="E311" s="10" t="n"/>
+    </row>
+    <row r="312">
+      <c r="E312" s="10" t="n"/>
+    </row>
+    <row r="313">
+      <c r="E313" s="10" t="n"/>
+    </row>
+    <row r="314">
+      <c r="E314" s="10" t="n"/>
+    </row>
+    <row r="315">
+      <c r="E315" s="10" t="n"/>
+    </row>
+    <row r="316">
+      <c r="E316" s="10" t="n"/>
+    </row>
+    <row r="317">
+      <c r="E317" s="10" t="n"/>
+    </row>
+    <row r="318">
+      <c r="E318" s="10" t="n"/>
+    </row>
+    <row r="319">
+      <c r="E319" s="10" t="n"/>
+    </row>
+    <row r="320">
+      <c r="E320" s="10" t="n"/>
+    </row>
+    <row r="321">
+      <c r="E321" s="10" t="n"/>
+    </row>
+    <row r="322">
+      <c r="E322" s="10" t="n"/>
+    </row>
+    <row r="323">
+      <c r="E323" s="10" t="n"/>
+    </row>
+    <row r="324">
+      <c r="E324" s="10" t="n"/>
+    </row>
+    <row r="325">
+      <c r="E325" s="10" t="n"/>
+    </row>
+    <row r="326">
+      <c r="E326" s="10" t="n"/>
+    </row>
+    <row r="327">
+      <c r="E327" s="10" t="n"/>
+    </row>
+    <row r="328">
+      <c r="E328" s="10" t="n"/>
+    </row>
+    <row r="329">
+      <c r="E329" s="10" t="n"/>
+    </row>
+    <row r="330">
+      <c r="E330" s="10" t="n"/>
+    </row>
+    <row r="331">
+      <c r="E331" s="10" t="n"/>
+    </row>
+    <row r="332">
+      <c r="E332" s="10" t="n"/>
+    </row>
+    <row r="333">
+      <c r="E333" s="10" t="n"/>
+    </row>
+    <row r="334">
+      <c r="E334" s="10" t="n"/>
+    </row>
+    <row r="335">
+      <c r="E335" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:E335"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="15" customWidth="1" style="4" min="1" max="1"/>
+    <col width="12" customWidth="1" style="4" min="2" max="2"/>
+    <col width="17.5" customWidth="1" style="4" min="3" max="3"/>
+    <col width="15.75" customWidth="1" style="4" min="4" max="4"/>
+    <col width="21.625" customWidth="1" style="4" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>드롭 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>아이템 TID</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>확률가중치</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>설명 (메모 — 로직 미사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ItemTable.ItemTID</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>DropTID</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ItemTID</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>201</v>
+      </c>
+      <c r="C10" t="n">
+        <v>20001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6590</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>밀</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>202</v>
+      </c>
+      <c r="C11" t="n">
+        <v>20002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>감자</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>203</v>
+      </c>
+      <c r="C12" t="n">
+        <v>20003</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>204</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20004</v>
+      </c>
+      <c r="D13" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>인삼</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>205</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20005</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>변종 인삼</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>206</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20006</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>태초의 씨앗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="E20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="E27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="E34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="E35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="E36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="E37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="E38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="E39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="E40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="E41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="E42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="E43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="E44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="E45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="E46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="E47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="E48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="E49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="E50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="E51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="E55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="E56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="E57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="E58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="E59" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="E60" s="10" t="n"/>
+    </row>
+    <row r="61">
+      <c r="E61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="E62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="E63" s="10" t="n"/>
+    </row>
+    <row r="64">
+      <c r="E64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="E65" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="E66" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="E67" s="10" t="n"/>
+    </row>
+    <row r="68">
+      <c r="E68" s="10" t="n"/>
+    </row>
+    <row r="69">
+      <c r="E69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="E70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="E71" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="E72" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="E73" s="10" t="n"/>
+    </row>
+    <row r="74">
+      <c r="E74" s="10" t="n"/>
+    </row>
+    <row r="75">
+      <c r="E75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="E76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="E77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="E78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="E79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="E80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="E81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="E82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="E83" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="E84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="E85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="E87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="E88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="E89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="E90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="E91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="E92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="E93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="E94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="E95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="E96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="E97" s="10" t="n"/>
+    </row>
+    <row r="98">
+      <c r="E98" s="10" t="n"/>
+    </row>
+    <row r="99">
+      <c r="E99" s="10" t="n"/>
+    </row>
+    <row r="100">
+      <c r="E100" s="10" t="n"/>
+    </row>
+    <row r="101">
+      <c r="E101" s="10" t="n"/>
+    </row>
+    <row r="102">
+      <c r="E102" s="10" t="n"/>
+    </row>
+    <row r="103">
+      <c r="E103" s="10" t="n"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="10" t="n"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="10" t="n"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="10" t="n"/>
+    </row>
+    <row r="107">
+      <c r="E107" s="10" t="n"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="10" t="n"/>
+    </row>
+    <row r="109">
+      <c r="E109" s="10" t="n"/>
+    </row>
+    <row r="110">
+      <c r="E110" s="10" t="n"/>
+    </row>
+    <row r="111">
+      <c r="E111" s="10" t="n"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="10" t="n"/>
+    </row>
+    <row r="113">
+      <c r="E113" s="10" t="n"/>
+    </row>
+    <row r="114">
+      <c r="E114" s="10" t="n"/>
+    </row>
+    <row r="115">
+      <c r="E115" s="10" t="n"/>
+    </row>
+    <row r="116">
+      <c r="E116" s="10" t="n"/>
+    </row>
+    <row r="117">
+      <c r="E117" s="10" t="n"/>
+    </row>
+    <row r="118">
+      <c r="E118" s="10" t="n"/>
+    </row>
+    <row r="119">
+      <c r="E119" s="10" t="n"/>
+    </row>
+    <row r="120">
+      <c r="E120" s="10" t="n"/>
+    </row>
+    <row r="121">
+      <c r="E121" s="10" t="n"/>
+    </row>
+    <row r="122">
+      <c r="E122" s="10" t="n"/>
+    </row>
+    <row r="123">
+      <c r="E123" s="10" t="n"/>
+    </row>
+    <row r="124">
+      <c r="E124" s="10" t="n"/>
+    </row>
+    <row r="125">
+      <c r="E125" s="10" t="n"/>
+    </row>
+    <row r="126">
+      <c r="E126" s="10" t="n"/>
+    </row>
+    <row r="127">
+      <c r="E127" s="10" t="n"/>
+    </row>
+    <row r="128">
+      <c r="E128" s="10" t="n"/>
+    </row>
+    <row r="129">
+      <c r="E129" s="10" t="n"/>
+    </row>
+    <row r="130">
+      <c r="E130" s="10" t="n"/>
+    </row>
+    <row r="131">
+      <c r="E131" s="10" t="n"/>
+    </row>
+    <row r="132">
+      <c r="E132" s="10" t="n"/>
+    </row>
+    <row r="133">
+      <c r="E133" s="10" t="n"/>
+    </row>
+    <row r="134">
+      <c r="E134" s="10" t="n"/>
+    </row>
+    <row r="135">
+      <c r="E135" s="10" t="n"/>
+    </row>
+    <row r="136">
+      <c r="E136" s="10" t="n"/>
+    </row>
+    <row r="137">
+      <c r="E137" s="10" t="n"/>
+    </row>
+    <row r="138">
+      <c r="E138" s="10" t="n"/>
+    </row>
+    <row r="139">
+      <c r="E139" s="10" t="n"/>
+    </row>
+    <row r="140">
+      <c r="E140" s="10" t="n"/>
+    </row>
+    <row r="141">
+      <c r="E141" s="10" t="n"/>
+    </row>
+    <row r="142">
+      <c r="E142" s="10" t="n"/>
+    </row>
+    <row r="143">
+      <c r="E143" s="10" t="n"/>
+    </row>
+    <row r="144">
+      <c r="E144" s="10" t="n"/>
+    </row>
+    <row r="145">
+      <c r="E145" s="10" t="n"/>
+    </row>
+    <row r="146">
+      <c r="E146" s="10" t="n"/>
+    </row>
+    <row r="147">
+      <c r="E147" s="10" t="n"/>
+    </row>
+    <row r="148">
+      <c r="E148" s="10" t="n"/>
+    </row>
+    <row r="149">
+      <c r="E149" s="10" t="n"/>
+    </row>
+    <row r="150">
+      <c r="E150" s="10" t="n"/>
+    </row>
+    <row r="151">
+      <c r="E151" s="10" t="n"/>
+    </row>
+    <row r="152">
+      <c r="E152" s="10" t="n"/>
+    </row>
+    <row r="153">
+      <c r="E153" s="10" t="n"/>
+    </row>
+    <row r="154">
+      <c r="E154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="E155" s="10" t="n"/>
+    </row>
+    <row r="156">
+      <c r="E156" s="10" t="n"/>
+    </row>
+    <row r="157">
+      <c r="E157" s="10" t="n"/>
+    </row>
+    <row r="158">
+      <c r="E158" s="10" t="n"/>
+    </row>
+    <row r="159">
+      <c r="E159" s="10" t="n"/>
+    </row>
+    <row r="160">
+      <c r="E160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="E161" s="10" t="n"/>
+    </row>
+    <row r="162">
+      <c r="E162" s="10" t="n"/>
+    </row>
+    <row r="163">
+      <c r="E163" s="10" t="n"/>
+    </row>
+    <row r="164">
+      <c r="E164" s="10" t="n"/>
+    </row>
+    <row r="165">
+      <c r="E165" s="10" t="n"/>
+    </row>
+    <row r="166">
+      <c r="E166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="E167" s="10" t="n"/>
+    </row>
+    <row r="168">
+      <c r="E168" s="10" t="n"/>
+    </row>
+    <row r="169">
+      <c r="E169" s="10" t="n"/>
+    </row>
+    <row r="170">
+      <c r="E170" s="10" t="n"/>
+    </row>
+    <row r="171">
+      <c r="E171" s="10" t="n"/>
+    </row>
+    <row r="172">
+      <c r="E172" s="10" t="n"/>
+    </row>
+    <row r="173">
+      <c r="E173" s="10" t="n"/>
+    </row>
+    <row r="174">
+      <c r="E174" s="10" t="n"/>
+    </row>
+    <row r="175">
+      <c r="E175" s="10" t="n"/>
+    </row>
+    <row r="176">
+      <c r="E176" s="10" t="n"/>
+    </row>
+    <row r="177">
+      <c r="E177" s="10" t="n"/>
+    </row>
+    <row r="178">
+      <c r="E178" s="10" t="n"/>
+    </row>
+    <row r="179">
+      <c r="E179" s="10" t="n"/>
+    </row>
+    <row r="180">
+      <c r="E180" s="10" t="n"/>
+    </row>
+    <row r="181">
+      <c r="E181" s="10" t="n"/>
+    </row>
+    <row r="182">
+      <c r="E182" s="10" t="n"/>
+    </row>
+    <row r="183">
+      <c r="E183" s="10" t="n"/>
+    </row>
+    <row r="184">
+      <c r="E184" s="10" t="n"/>
+    </row>
+    <row r="185">
+      <c r="E185" s="10" t="n"/>
+    </row>
+    <row r="186">
+      <c r="E186" s="10" t="n"/>
+    </row>
+    <row r="187">
+      <c r="E187" s="10" t="n"/>
+    </row>
+    <row r="188">
+      <c r="E188" s="10" t="n"/>
+    </row>
+    <row r="189">
+      <c r="E189" s="10" t="n"/>
+    </row>
+    <row r="190">
+      <c r="E190" s="10" t="n"/>
+    </row>
+    <row r="191">
+      <c r="E191" s="10" t="n"/>
+    </row>
+    <row r="192">
+      <c r="E192" s="10" t="n"/>
+    </row>
+    <row r="193">
+      <c r="E193" s="10" t="n"/>
+    </row>
+    <row r="194">
+      <c r="E194" s="10" t="n"/>
+    </row>
+    <row r="195">
+      <c r="E195" s="10" t="n"/>
+    </row>
+    <row r="196">
+      <c r="E196" s="10" t="n"/>
+    </row>
+    <row r="197">
+      <c r="E197" s="10" t="n"/>
+    </row>
+    <row r="198">
+      <c r="E198" s="10" t="n"/>
+    </row>
+    <row r="199">
+      <c r="E199" s="10" t="n"/>
+    </row>
+    <row r="200">
+      <c r="E200" s="10" t="n"/>
+    </row>
+    <row r="201">
+      <c r="E201" s="10" t="n"/>
+    </row>
+    <row r="202">
+      <c r="E202" s="10" t="n"/>
+    </row>
+    <row r="203">
+      <c r="E203" s="10" t="n"/>
+    </row>
+    <row r="204">
+      <c r="E204" s="10" t="n"/>
+    </row>
+    <row r="205">
+      <c r="E205" s="10" t="n"/>
+    </row>
+    <row r="206">
+      <c r="E206" s="10" t="n"/>
+    </row>
+    <row r="207">
+      <c r="E207" s="10" t="n"/>
+    </row>
+    <row r="208">
+      <c r="E208" s="10" t="n"/>
+    </row>
+    <row r="209">
+      <c r="E209" s="10" t="n"/>
+    </row>
+    <row r="210">
+      <c r="E210" s="10" t="n"/>
+    </row>
+    <row r="211">
+      <c r="E211" s="10" t="n"/>
+    </row>
+    <row r="212">
+      <c r="E212" s="10" t="n"/>
+    </row>
+    <row r="213">
+      <c r="E213" s="10" t="n"/>
+    </row>
+    <row r="214">
+      <c r="E214" s="10" t="n"/>
+    </row>
+    <row r="215">
+      <c r="E215" s="10" t="n"/>
+    </row>
+    <row r="216">
+      <c r="E216" s="10" t="n"/>
+    </row>
+    <row r="217">
+      <c r="E217" s="10" t="n"/>
+    </row>
+    <row r="218">
+      <c r="E218" s="10" t="n"/>
+    </row>
+    <row r="219">
+      <c r="E219" s="10" t="n"/>
+    </row>
+    <row r="220">
+      <c r="E220" s="10" t="n"/>
+    </row>
+    <row r="221">
+      <c r="E221" s="10" t="n"/>
+    </row>
+    <row r="222">
+      <c r="E222" s="10" t="n"/>
+    </row>
+    <row r="223">
+      <c r="E223" s="10" t="n"/>
+    </row>
+    <row r="224">
+      <c r="E224" s="10" t="n"/>
+    </row>
+    <row r="225">
+      <c r="E225" s="10" t="n"/>
+    </row>
+    <row r="226">
+      <c r="E226" s="10" t="n"/>
+    </row>
+    <row r="227">
+      <c r="E227" s="10" t="n"/>
+    </row>
+    <row r="228">
+      <c r="E228" s="10" t="n"/>
+    </row>
+    <row r="229">
+      <c r="E229" s="10" t="n"/>
+    </row>
+    <row r="230">
+      <c r="E230" s="10" t="n"/>
+    </row>
+    <row r="231">
+      <c r="E231" s="10" t="n"/>
+    </row>
+    <row r="232">
+      <c r="E232" s="10" t="n"/>
+    </row>
+    <row r="233">
+      <c r="E233" s="10" t="n"/>
+    </row>
+    <row r="234">
+      <c r="E234" s="10" t="n"/>
+    </row>
+    <row r="235">
+      <c r="E235" s="10" t="n"/>
+    </row>
+    <row r="236">
+      <c r="E236" s="10" t="n"/>
+    </row>
+    <row r="237">
+      <c r="E237" s="10" t="n"/>
+    </row>
+    <row r="238">
+      <c r="E238" s="10" t="n"/>
+    </row>
+    <row r="239">
+      <c r="E239" s="10" t="n"/>
+    </row>
+    <row r="240">
+      <c r="E240" s="10" t="n"/>
+    </row>
+    <row r="241">
+      <c r="E241" s="10" t="n"/>
+    </row>
+    <row r="242">
+      <c r="E242" s="10" t="n"/>
+    </row>
+    <row r="243">
+      <c r="E243" s="10" t="n"/>
+    </row>
+    <row r="244">
+      <c r="E244" s="10" t="n"/>
+    </row>
+    <row r="245">
+      <c r="E245" s="10" t="n"/>
+    </row>
+    <row r="246">
+      <c r="E246" s="10" t="n"/>
+    </row>
+    <row r="247">
+      <c r="E247" s="10" t="n"/>
+    </row>
+    <row r="248">
+      <c r="E248" s="10" t="n"/>
+    </row>
+    <row r="249">
+      <c r="E249" s="10" t="n"/>
+    </row>
+    <row r="250">
+      <c r="E250" s="10" t="n"/>
+    </row>
+    <row r="251">
+      <c r="E251" s="10" t="n"/>
+    </row>
+    <row r="252">
+      <c r="E252" s="10" t="n"/>
+    </row>
+    <row r="253">
+      <c r="E253" s="10" t="n"/>
+    </row>
+    <row r="254">
+      <c r="E254" s="10" t="n"/>
+    </row>
+    <row r="255">
+      <c r="E255" s="10" t="n"/>
+    </row>
+    <row r="256">
+      <c r="E256" s="10" t="n"/>
+    </row>
+    <row r="257">
+      <c r="E257" s="10" t="n"/>
+    </row>
+    <row r="258">
+      <c r="E258" s="10" t="n"/>
+    </row>
+    <row r="259">
+      <c r="E259" s="10" t="n"/>
+    </row>
+    <row r="260">
+      <c r="E260" s="10" t="n"/>
+    </row>
+    <row r="261">
+      <c r="E261" s="10" t="n"/>
+    </row>
+    <row r="262">
+      <c r="E262" s="10" t="n"/>
+    </row>
+    <row r="263">
+      <c r="E263" s="10" t="n"/>
+    </row>
+    <row r="264">
+      <c r="E264" s="10" t="n"/>
+    </row>
+    <row r="265">
+      <c r="E265" s="10" t="n"/>
+    </row>
+    <row r="266">
+      <c r="E266" s="10" t="n"/>
+    </row>
+    <row r="267">
+      <c r="E267" s="10" t="n"/>
+    </row>
+    <row r="268">
+      <c r="E268" s="10" t="n"/>
+    </row>
+    <row r="269">
+      <c r="E269" s="10" t="n"/>
+    </row>
+    <row r="270">
+      <c r="E270" s="10" t="n"/>
+    </row>
+    <row r="271">
+      <c r="E271" s="10" t="n"/>
+    </row>
+    <row r="272">
+      <c r="E272" s="10" t="n"/>
+    </row>
+    <row r="273">
+      <c r="E273" s="10" t="n"/>
+    </row>
+    <row r="274">
+      <c r="E274" s="10" t="n"/>
+    </row>
+    <row r="275">
+      <c r="E275" s="10" t="n"/>
+    </row>
+    <row r="276">
+      <c r="E276" s="10" t="n"/>
+    </row>
+    <row r="277">
+      <c r="E277" s="10" t="n"/>
+    </row>
+    <row r="278">
+      <c r="E278" s="10" t="n"/>
+    </row>
+    <row r="279">
+      <c r="E279" s="10" t="n"/>
+    </row>
+    <row r="280">
+      <c r="E280" s="10" t="n"/>
+    </row>
+    <row r="281">
+      <c r="E281" s="10" t="n"/>
+    </row>
+    <row r="282">
+      <c r="E282" s="10" t="n"/>
+    </row>
+    <row r="283">
+      <c r="E283" s="10" t="n"/>
+    </row>
+    <row r="284">
+      <c r="E284" s="10" t="n"/>
+    </row>
+    <row r="285">
+      <c r="E285" s="10" t="n"/>
+    </row>
+    <row r="286">
+      <c r="E286" s="10" t="n"/>
+    </row>
+    <row r="287">
+      <c r="E287" s="10" t="n"/>
+    </row>
+    <row r="288">
+      <c r="E288" s="10" t="n"/>
+    </row>
+    <row r="289">
+      <c r="E289" s="10" t="n"/>
+    </row>
+    <row r="290">
+      <c r="E290" s="10" t="n"/>
+    </row>
+    <row r="291">
+      <c r="E291" s="10" t="n"/>
+    </row>
+    <row r="292">
+      <c r="E292" s="10" t="n"/>
+    </row>
+    <row r="293">
+      <c r="E293" s="10" t="n"/>
+    </row>
+    <row r="294">
+      <c r="E294" s="10" t="n"/>
+    </row>
+    <row r="295">
+      <c r="E295" s="10" t="n"/>
+    </row>
+    <row r="296">
+      <c r="E296" s="10" t="n"/>
+    </row>
+    <row r="297">
+      <c r="E297" s="10" t="n"/>
+    </row>
+    <row r="298">
+      <c r="E298" s="10" t="n"/>
+    </row>
+    <row r="299">
+      <c r="E299" s="10" t="n"/>
+    </row>
+    <row r="300">
+      <c r="E300" s="10" t="n"/>
+    </row>
+    <row r="301">
+      <c r="E301" s="10" t="n"/>
+    </row>
+    <row r="302">
+      <c r="E302" s="10" t="n"/>
+    </row>
+    <row r="303">
+      <c r="E303" s="10" t="n"/>
+    </row>
+    <row r="304">
+      <c r="E304" s="10" t="n"/>
+    </row>
+    <row r="305">
+      <c r="E305" s="10" t="n"/>
+    </row>
+    <row r="306">
+      <c r="E306" s="10" t="n"/>
+    </row>
+    <row r="307">
+      <c r="E307" s="10" t="n"/>
+    </row>
+    <row r="308">
+      <c r="E308" s="10" t="n"/>
+    </row>
+    <row r="309">
+      <c r="E309" s="10" t="n"/>
+    </row>
+    <row r="310">
+      <c r="E310" s="10" t="n"/>
+    </row>
+    <row r="311">
+      <c r="E311" s="10" t="n"/>
+    </row>
+    <row r="312">
+      <c r="E312" s="10" t="n"/>
+    </row>
+    <row r="313">
+      <c r="E313" s="10" t="n"/>
+    </row>
+    <row r="314">
+      <c r="E314" s="10" t="n"/>
+    </row>
+    <row r="315">
+      <c r="E315" s="10" t="n"/>
+    </row>
+    <row r="316">
+      <c r="E316" s="10" t="n"/>
+    </row>
+    <row r="317">
+      <c r="E317" s="10" t="n"/>
+    </row>
+    <row r="318">
+      <c r="E318" s="10" t="n"/>
+    </row>
+    <row r="319">
+      <c r="E319" s="10" t="n"/>
+    </row>
+    <row r="320">
+      <c r="E320" s="10" t="n"/>
+    </row>
+    <row r="321">
+      <c r="E321" s="10" t="n"/>
+    </row>
+    <row r="322">
+      <c r="E322" s="10" t="n"/>
+    </row>
+    <row r="323">
+      <c r="E323" s="10" t="n"/>
+    </row>
+    <row r="324">
+      <c r="E324" s="10" t="n"/>
+    </row>
+    <row r="325">
+      <c r="E325" s="10" t="n"/>
+    </row>
+    <row r="326">
+      <c r="E326" s="10" t="n"/>
+    </row>
+    <row r="327">
+      <c r="E327" s="10" t="n"/>
+    </row>
+    <row r="328">
+      <c r="E328" s="10" t="n"/>
+    </row>
+    <row r="329">
+      <c r="E329" s="10" t="n"/>
+    </row>
+    <row r="330">
+      <c r="E330" s="10" t="n"/>
+    </row>
+    <row r="331">
+      <c r="E331" s="10" t="n"/>
+    </row>
+    <row r="332">
+      <c r="E332" s="10" t="n"/>
+    </row>
+    <row r="333">
+      <c r="E333" s="10" t="n"/>
+    </row>
+    <row r="334">
+      <c r="E334" s="10" t="n"/>
+    </row>
+    <row r="335">
+      <c r="E335" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:E335"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="15" customWidth="1" style="4" min="1" max="1"/>
+    <col width="12" customWidth="1" style="4" min="2" max="2"/>
+    <col width="17.5" customWidth="1" style="4" min="3" max="3"/>
+    <col width="15.75" customWidth="1" style="4" min="4" max="4"/>
+    <col width="21.625" customWidth="1" style="4" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>드롭 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>아이템 TID</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>확률가중치</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>설명 (메모 — 로직 미사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ItemTable.ItemTID</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>DropTID</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ItemTID</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>301</v>
+      </c>
+      <c r="C10" t="n">
+        <v>30001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6590</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>잡목</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>302</v>
+      </c>
+      <c r="C11" t="n">
+        <v>30002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>소나무 목재</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>303</v>
+      </c>
+      <c r="C12" t="n">
+        <v>30003</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>참나무 목재</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>304</v>
+      </c>
+      <c r="C13" t="n">
+        <v>30004</v>
+      </c>
+      <c r="D13" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>흑단 목재</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>305</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30005</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>고급 원목</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>306</v>
+      </c>
+      <c r="C15" t="n">
+        <v>30006</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>세계수 가지</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="E20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="E27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="E34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="E35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="E36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="E37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="E38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="E39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="E40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="E41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="E42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="E43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="E44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="E45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="E46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="E47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="E48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="E49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="E50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="E51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="E55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="E56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="E57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="E58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="E59" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="E60" s="10" t="n"/>
+    </row>
+    <row r="61">
+      <c r="E61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="E62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="E63" s="10" t="n"/>
+    </row>
+    <row r="64">
+      <c r="E64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="E65" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="E66" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="E67" s="10" t="n"/>
+    </row>
+    <row r="68">
+      <c r="E68" s="10" t="n"/>
+    </row>
+    <row r="69">
+      <c r="E69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="E70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="E71" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="E72" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="E73" s="10" t="n"/>
+    </row>
+    <row r="74">
+      <c r="E74" s="10" t="n"/>
+    </row>
+    <row r="75">
+      <c r="E75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="E76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="E77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="E78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="E79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="E80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="E81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="E82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="E83" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="E84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="E85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="E87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="E88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="E89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="E90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="E91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="E92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="E93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="E94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="E95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="E96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="E97" s="10" t="n"/>
+    </row>
+    <row r="98">
+      <c r="E98" s="10" t="n"/>
+    </row>
+    <row r="99">
+      <c r="E99" s="10" t="n"/>
+    </row>
+    <row r="100">
+      <c r="E100" s="10" t="n"/>
+    </row>
+    <row r="101">
+      <c r="E101" s="10" t="n"/>
+    </row>
+    <row r="102">
+      <c r="E102" s="10" t="n"/>
+    </row>
+    <row r="103">
+      <c r="E103" s="10" t="n"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="10" t="n"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="10" t="n"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="10" t="n"/>
+    </row>
+    <row r="107">
+      <c r="E107" s="10" t="n"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="10" t="n"/>
+    </row>
+    <row r="109">
+      <c r="E109" s="10" t="n"/>
+    </row>
+    <row r="110">
+      <c r="E110" s="10" t="n"/>
+    </row>
+    <row r="111">
+      <c r="E111" s="10" t="n"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="10" t="n"/>
+    </row>
+    <row r="113">
+      <c r="E113" s="10" t="n"/>
+    </row>
+    <row r="114">
+      <c r="E114" s="10" t="n"/>
+    </row>
+    <row r="115">
+      <c r="E115" s="10" t="n"/>
+    </row>
+    <row r="116">
+      <c r="E116" s="10" t="n"/>
+    </row>
+    <row r="117">
+      <c r="E117" s="10" t="n"/>
+    </row>
+    <row r="118">
+      <c r="E118" s="10" t="n"/>
+    </row>
+    <row r="119">
+      <c r="E119" s="10" t="n"/>
+    </row>
+    <row r="120">
+      <c r="E120" s="10" t="n"/>
+    </row>
+    <row r="121">
+      <c r="E121" s="10" t="n"/>
+    </row>
+    <row r="122">
+      <c r="E122" s="10" t="n"/>
+    </row>
+    <row r="123">
+      <c r="E123" s="10" t="n"/>
+    </row>
+    <row r="124">
+      <c r="E124" s="10" t="n"/>
+    </row>
+    <row r="125">
+      <c r="E125" s="10" t="n"/>
+    </row>
+    <row r="126">
+      <c r="E126" s="10" t="n"/>
+    </row>
+    <row r="127">
+      <c r="E127" s="10" t="n"/>
+    </row>
+    <row r="128">
+      <c r="E128" s="10" t="n"/>
+    </row>
+    <row r="129">
+      <c r="E129" s="10" t="n"/>
+    </row>
+    <row r="130">
+      <c r="E130" s="10" t="n"/>
+    </row>
+    <row r="131">
+      <c r="E131" s="10" t="n"/>
+    </row>
+    <row r="132">
+      <c r="E132" s="10" t="n"/>
+    </row>
+    <row r="133">
+      <c r="E133" s="10" t="n"/>
+    </row>
+    <row r="134">
+      <c r="E134" s="10" t="n"/>
+    </row>
+    <row r="135">
+      <c r="E135" s="10" t="n"/>
+    </row>
+    <row r="136">
+      <c r="E136" s="10" t="n"/>
+    </row>
+    <row r="137">
+      <c r="E137" s="10" t="n"/>
+    </row>
+    <row r="138">
+      <c r="E138" s="10" t="n"/>
+    </row>
+    <row r="139">
+      <c r="E139" s="10" t="n"/>
+    </row>
+    <row r="140">
+      <c r="E140" s="10" t="n"/>
+    </row>
+    <row r="141">
+      <c r="E141" s="10" t="n"/>
+    </row>
+    <row r="142">
+      <c r="E142" s="10" t="n"/>
+    </row>
+    <row r="143">
+      <c r="E143" s="10" t="n"/>
+    </row>
+    <row r="144">
+      <c r="E144" s="10" t="n"/>
+    </row>
+    <row r="145">
+      <c r="E145" s="10" t="n"/>
+    </row>
+    <row r="146">
+      <c r="E146" s="10" t="n"/>
+    </row>
+    <row r="147">
+      <c r="E147" s="10" t="n"/>
+    </row>
+    <row r="148">
+      <c r="E148" s="10" t="n"/>
+    </row>
+    <row r="149">
+      <c r="E149" s="10" t="n"/>
+    </row>
+    <row r="150">
+      <c r="E150" s="10" t="n"/>
+    </row>
+    <row r="151">
+      <c r="E151" s="10" t="n"/>
+    </row>
+    <row r="152">
+      <c r="E152" s="10" t="n"/>
+    </row>
+    <row r="153">
+      <c r="E153" s="10" t="n"/>
+    </row>
+    <row r="154">
+      <c r="E154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="E155" s="10" t="n"/>
+    </row>
+    <row r="156">
+      <c r="E156" s="10" t="n"/>
+    </row>
+    <row r="157">
+      <c r="E157" s="10" t="n"/>
+    </row>
+    <row r="158">
+      <c r="E158" s="10" t="n"/>
+    </row>
+    <row r="159">
+      <c r="E159" s="10" t="n"/>
+    </row>
+    <row r="160">
+      <c r="E160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="E161" s="10" t="n"/>
+    </row>
+    <row r="162">
+      <c r="E162" s="10" t="n"/>
+    </row>
+    <row r="163">
+      <c r="E163" s="10" t="n"/>
+    </row>
+    <row r="164">
+      <c r="E164" s="10" t="n"/>
+    </row>
+    <row r="165">
+      <c r="E165" s="10" t="n"/>
+    </row>
+    <row r="166">
+      <c r="E166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="E167" s="10" t="n"/>
+    </row>
+    <row r="168">
+      <c r="E168" s="10" t="n"/>
+    </row>
+    <row r="169">
+      <c r="E169" s="10" t="n"/>
+    </row>
+    <row r="170">
+      <c r="E170" s="10" t="n"/>
+    </row>
+    <row r="171">
+      <c r="E171" s="10" t="n"/>
+    </row>
+    <row r="172">
+      <c r="E172" s="10" t="n"/>
+    </row>
+    <row r="173">
+      <c r="E173" s="10" t="n"/>
+    </row>
+    <row r="174">
+      <c r="E174" s="10" t="n"/>
+    </row>
+    <row r="175">
+      <c r="E175" s="10" t="n"/>
+    </row>
+    <row r="176">
+      <c r="E176" s="10" t="n"/>
+    </row>
+    <row r="177">
+      <c r="E177" s="10" t="n"/>
+    </row>
+    <row r="178">
+      <c r="E178" s="10" t="n"/>
+    </row>
+    <row r="179">
+      <c r="E179" s="10" t="n"/>
+    </row>
+    <row r="180">
+      <c r="E180" s="10" t="n"/>
+    </row>
+    <row r="181">
+      <c r="E181" s="10" t="n"/>
+    </row>
+    <row r="182">
+      <c r="E182" s="10" t="n"/>
+    </row>
+    <row r="183">
+      <c r="E183" s="10" t="n"/>
+    </row>
+    <row r="184">
+      <c r="E184" s="10" t="n"/>
+    </row>
+    <row r="185">
+      <c r="E185" s="10" t="n"/>
+    </row>
+    <row r="186">
+      <c r="E186" s="10" t="n"/>
+    </row>
+    <row r="187">
+      <c r="E187" s="10" t="n"/>
+    </row>
+    <row r="188">
+      <c r="E188" s="10" t="n"/>
+    </row>
+    <row r="189">
+      <c r="E189" s="10" t="n"/>
+    </row>
+    <row r="190">
+      <c r="E190" s="10" t="n"/>
+    </row>
+    <row r="191">
+      <c r="E191" s="10" t="n"/>
+    </row>
+    <row r="192">
+      <c r="E192" s="10" t="n"/>
+    </row>
+    <row r="193">
+      <c r="E193" s="10" t="n"/>
+    </row>
+    <row r="194">
+      <c r="E194" s="10" t="n"/>
+    </row>
+    <row r="195">
+      <c r="E195" s="10" t="n"/>
+    </row>
+    <row r="196">
+      <c r="E196" s="10" t="n"/>
+    </row>
+    <row r="197">
+      <c r="E197" s="10" t="n"/>
+    </row>
+    <row r="198">
+      <c r="E198" s="10" t="n"/>
+    </row>
+    <row r="199">
+      <c r="E199" s="10" t="n"/>
+    </row>
+    <row r="200">
+      <c r="E200" s="10" t="n"/>
+    </row>
+    <row r="201">
+      <c r="E201" s="10" t="n"/>
+    </row>
+    <row r="202">
+      <c r="E202" s="10" t="n"/>
+    </row>
+    <row r="203">
+      <c r="E203" s="10" t="n"/>
+    </row>
+    <row r="204">
+      <c r="E204" s="10" t="n"/>
+    </row>
+    <row r="205">
+      <c r="E205" s="10" t="n"/>
+    </row>
+    <row r="206">
+      <c r="E206" s="10" t="n"/>
+    </row>
+    <row r="207">
+      <c r="E207" s="10" t="n"/>
+    </row>
+    <row r="208">
+      <c r="E208" s="10" t="n"/>
+    </row>
+    <row r="209">
+      <c r="E209" s="10" t="n"/>
+    </row>
+    <row r="210">
+      <c r="E210" s="10" t="n"/>
+    </row>
+    <row r="211">
+      <c r="E211" s="10" t="n"/>
+    </row>
+    <row r="212">
+      <c r="E212" s="10" t="n"/>
+    </row>
+    <row r="213">
+      <c r="E213" s="10" t="n"/>
+    </row>
+    <row r="214">
+      <c r="E214" s="10" t="n"/>
+    </row>
+    <row r="215">
+      <c r="E215" s="10" t="n"/>
+    </row>
+    <row r="216">
+      <c r="E216" s="10" t="n"/>
+    </row>
+    <row r="217">
+      <c r="E217" s="10" t="n"/>
+    </row>
+    <row r="218">
+      <c r="E218" s="10" t="n"/>
+    </row>
+    <row r="219">
+      <c r="E219" s="10" t="n"/>
+    </row>
+    <row r="220">
+      <c r="E220" s="10" t="n"/>
+    </row>
+    <row r="221">
+      <c r="E221" s="10" t="n"/>
+    </row>
+    <row r="222">
+      <c r="E222" s="10" t="n"/>
+    </row>
+    <row r="223">
+      <c r="E223" s="10" t="n"/>
+    </row>
+    <row r="224">
+      <c r="E224" s="10" t="n"/>
+    </row>
+    <row r="225">
+      <c r="E225" s="10" t="n"/>
+    </row>
+    <row r="226">
+      <c r="E226" s="10" t="n"/>
+    </row>
+    <row r="227">
+      <c r="E227" s="10" t="n"/>
+    </row>
+    <row r="228">
+      <c r="E228" s="10" t="n"/>
+    </row>
+    <row r="229">
+      <c r="E229" s="10" t="n"/>
+    </row>
+    <row r="230">
+      <c r="E230" s="10" t="n"/>
+    </row>
+    <row r="231">
+      <c r="E231" s="10" t="n"/>
+    </row>
+    <row r="232">
+      <c r="E232" s="10" t="n"/>
+    </row>
+    <row r="233">
+      <c r="E233" s="10" t="n"/>
+    </row>
+    <row r="234">
+      <c r="E234" s="10" t="n"/>
+    </row>
+    <row r="235">
+      <c r="E235" s="10" t="n"/>
+    </row>
+    <row r="236">
+      <c r="E236" s="10" t="n"/>
+    </row>
+    <row r="237">
+      <c r="E237" s="10" t="n"/>
+    </row>
+    <row r="238">
+      <c r="E238" s="10" t="n"/>
+    </row>
+    <row r="239">
+      <c r="E239" s="10" t="n"/>
+    </row>
+    <row r="240">
+      <c r="E240" s="10" t="n"/>
+    </row>
+    <row r="241">
+      <c r="E241" s="10" t="n"/>
+    </row>
+    <row r="242">
+      <c r="E242" s="10" t="n"/>
+    </row>
+    <row r="243">
+      <c r="E243" s="10" t="n"/>
+    </row>
+    <row r="244">
+      <c r="E244" s="10" t="n"/>
+    </row>
+    <row r="245">
+      <c r="E245" s="10" t="n"/>
+    </row>
+    <row r="246">
+      <c r="E246" s="10" t="n"/>
+    </row>
+    <row r="247">
+      <c r="E247" s="10" t="n"/>
+    </row>
+    <row r="248">
+      <c r="E248" s="10" t="n"/>
+    </row>
+    <row r="249">
+      <c r="E249" s="10" t="n"/>
+    </row>
+    <row r="250">
+      <c r="E250" s="10" t="n"/>
+    </row>
+    <row r="251">
+      <c r="E251" s="10" t="n"/>
+    </row>
+    <row r="252">
+      <c r="E252" s="10" t="n"/>
+    </row>
+    <row r="253">
+      <c r="E253" s="10" t="n"/>
+    </row>
+    <row r="254">
+      <c r="E254" s="10" t="n"/>
+    </row>
+    <row r="255">
+      <c r="E255" s="10" t="n"/>
+    </row>
+    <row r="256">
+      <c r="E256" s="10" t="n"/>
+    </row>
+    <row r="257">
+      <c r="E257" s="10" t="n"/>
+    </row>
+    <row r="258">
+      <c r="E258" s="10" t="n"/>
+    </row>
+    <row r="259">
+      <c r="E259" s="10" t="n"/>
+    </row>
+    <row r="260">
+      <c r="E260" s="10" t="n"/>
+    </row>
+    <row r="261">
+      <c r="E261" s="10" t="n"/>
+    </row>
+    <row r="262">
+      <c r="E262" s="10" t="n"/>
+    </row>
+    <row r="263">
+      <c r="E263" s="10" t="n"/>
+    </row>
+    <row r="264">
+      <c r="E264" s="10" t="n"/>
+    </row>
+    <row r="265">
+      <c r="E265" s="10" t="n"/>
+    </row>
+    <row r="266">
+      <c r="E266" s="10" t="n"/>
+    </row>
+    <row r="267">
+      <c r="E267" s="10" t="n"/>
+    </row>
+    <row r="268">
+      <c r="E268" s="10" t="n"/>
+    </row>
+    <row r="269">
+      <c r="E269" s="10" t="n"/>
+    </row>
+    <row r="270">
+      <c r="E270" s="10" t="n"/>
+    </row>
+    <row r="271">
+      <c r="E271" s="10" t="n"/>
+    </row>
+    <row r="272">
+      <c r="E272" s="10" t="n"/>
+    </row>
+    <row r="273">
+      <c r="E273" s="10" t="n"/>
+    </row>
+    <row r="274">
+      <c r="E274" s="10" t="n"/>
+    </row>
+    <row r="275">
+      <c r="E275" s="10" t="n"/>
+    </row>
+    <row r="276">
+      <c r="E276" s="10" t="n"/>
+    </row>
+    <row r="277">
+      <c r="E277" s="10" t="n"/>
+    </row>
+    <row r="278">
+      <c r="E278" s="10" t="n"/>
+    </row>
+    <row r="279">
+      <c r="E279" s="10" t="n"/>
+    </row>
+    <row r="280">
+      <c r="E280" s="10" t="n"/>
+    </row>
+    <row r="281">
+      <c r="E281" s="10" t="n"/>
+    </row>
+    <row r="282">
+      <c r="E282" s="10" t="n"/>
+    </row>
+    <row r="283">
+      <c r="E283" s="10" t="n"/>
+    </row>
+    <row r="284">
+      <c r="E284" s="10" t="n"/>
+    </row>
+    <row r="285">
+      <c r="E285" s="10" t="n"/>
+    </row>
+    <row r="286">
+      <c r="E286" s="10" t="n"/>
+    </row>
+    <row r="287">
+      <c r="E287" s="10" t="n"/>
+    </row>
+    <row r="288">
+      <c r="E288" s="10" t="n"/>
+    </row>
+    <row r="289">
+      <c r="E289" s="10" t="n"/>
+    </row>
+    <row r="290">
+      <c r="E290" s="10" t="n"/>
+    </row>
+    <row r="291">
+      <c r="E291" s="10" t="n"/>
+    </row>
+    <row r="292">
+      <c r="E292" s="10" t="n"/>
+    </row>
+    <row r="293">
+      <c r="E293" s="10" t="n"/>
+    </row>
+    <row r="294">
+      <c r="E294" s="10" t="n"/>
+    </row>
+    <row r="295">
+      <c r="E295" s="10" t="n"/>
+    </row>
+    <row r="296">
+      <c r="E296" s="10" t="n"/>
+    </row>
+    <row r="297">
+      <c r="E297" s="10" t="n"/>
+    </row>
+    <row r="298">
+      <c r="E298" s="10" t="n"/>
+    </row>
+    <row r="299">
+      <c r="E299" s="10" t="n"/>
+    </row>
+    <row r="300">
+      <c r="E300" s="10" t="n"/>
+    </row>
+    <row r="301">
+      <c r="E301" s="10" t="n"/>
+    </row>
+    <row r="302">
+      <c r="E302" s="10" t="n"/>
+    </row>
+    <row r="303">
+      <c r="E303" s="10" t="n"/>
+    </row>
+    <row r="304">
+      <c r="E304" s="10" t="n"/>
+    </row>
+    <row r="305">
+      <c r="E305" s="10" t="n"/>
+    </row>
+    <row r="306">
+      <c r="E306" s="10" t="n"/>
+    </row>
+    <row r="307">
+      <c r="E307" s="10" t="n"/>
+    </row>
+    <row r="308">
+      <c r="E308" s="10" t="n"/>
+    </row>
+    <row r="309">
+      <c r="E309" s="10" t="n"/>
+    </row>
+    <row r="310">
+      <c r="E310" s="10" t="n"/>
+    </row>
+    <row r="311">
+      <c r="E311" s="10" t="n"/>
+    </row>
+    <row r="312">
+      <c r="E312" s="10" t="n"/>
+    </row>
+    <row r="313">
+      <c r="E313" s="10" t="n"/>
+    </row>
+    <row r="314">
+      <c r="E314" s="10" t="n"/>
+    </row>
+    <row r="315">
+      <c r="E315" s="10" t="n"/>
+    </row>
+    <row r="316">
+      <c r="E316" s="10" t="n"/>
+    </row>
+    <row r="317">
+      <c r="E317" s="10" t="n"/>
+    </row>
+    <row r="318">
+      <c r="E318" s="10" t="n"/>
+    </row>
+    <row r="319">
+      <c r="E319" s="10" t="n"/>
+    </row>
+    <row r="320">
+      <c r="E320" s="10" t="n"/>
+    </row>
+    <row r="321">
+      <c r="E321" s="10" t="n"/>
+    </row>
+    <row r="322">
+      <c r="E322" s="10" t="n"/>
+    </row>
+    <row r="323">
+      <c r="E323" s="10" t="n"/>
+    </row>
+    <row r="324">
+      <c r="E324" s="10" t="n"/>
+    </row>
+    <row r="325">
+      <c r="E325" s="10" t="n"/>
+    </row>
+    <row r="326">
+      <c r="E326" s="10" t="n"/>
+    </row>
+    <row r="327">
+      <c r="E327" s="10" t="n"/>
+    </row>
+    <row r="328">
+      <c r="E328" s="10" t="n"/>
+    </row>
+    <row r="329">
+      <c r="E329" s="10" t="n"/>
+    </row>
+    <row r="330">
+      <c r="E330" s="10" t="n"/>
+    </row>
+    <row r="331">
+      <c r="E331" s="10" t="n"/>
+    </row>
+    <row r="332">
+      <c r="E332" s="10" t="n"/>
+    </row>
+    <row r="333">
+      <c r="E333" s="10" t="n"/>
+    </row>
+    <row r="334">
+      <c r="E334" s="10" t="n"/>
+    </row>
+    <row r="335">
+      <c r="E335" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:E335"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="15" customWidth="1" style="4" min="1" max="1"/>
+    <col width="12" customWidth="1" style="4" min="2" max="2"/>
+    <col width="17.5" customWidth="1" style="4" min="3" max="3"/>
+    <col width="15.75" customWidth="1" style="4" min="4" max="4"/>
+    <col width="21.625" customWidth="1" style="4" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>드롭 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>아이템 TID</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>확률가중치</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>설명 (메모 — 로직 미사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ItemTable.ItemTID</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>DropTID</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ItemTID</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>401</v>
+      </c>
+      <c r="C10" t="n">
+        <v>40001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6590</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>돌덩어리</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>402</v>
+      </c>
+      <c r="C11" t="n">
+        <v>40002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>구리 광석</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>403</v>
+      </c>
+      <c r="C12" t="n">
+        <v>40003</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>은광석</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>404</v>
+      </c>
+      <c r="C13" t="n">
+        <v>40004</v>
+      </c>
+      <c r="D13" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>금광석</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>405</v>
+      </c>
+      <c r="C14" t="n">
+        <v>40005</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>보석 원석</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>406</v>
+      </c>
+      <c r="C15" t="n">
+        <v>40006</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>심연의 원석</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="E20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="E27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="E34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="E35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="E36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="E37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="E38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="E39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="E40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="E41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="E42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="E43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="E44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="E45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="E46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="E47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="E48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="E49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="E50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="E51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="E55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="E56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="E57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="E58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="E59" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="E60" s="10" t="n"/>
+    </row>
+    <row r="61">
+      <c r="E61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="E62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="E63" s="10" t="n"/>
+    </row>
+    <row r="64">
+      <c r="E64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="E65" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="E66" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="E67" s="10" t="n"/>
+    </row>
+    <row r="68">
+      <c r="E68" s="10" t="n"/>
+    </row>
+    <row r="69">
+      <c r="E69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="E70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="E71" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="E72" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="E73" s="10" t="n"/>
+    </row>
+    <row r="74">
+      <c r="E74" s="10" t="n"/>
+    </row>
+    <row r="75">
+      <c r="E75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="E76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="E77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="E78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="E79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="E80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="E81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="E82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="E83" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="E84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="E85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="E87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="E88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="E89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="E90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="E91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="E92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="E93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="E94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="E95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="E96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="E97" s="10" t="n"/>
+    </row>
+    <row r="98">
+      <c r="E98" s="10" t="n"/>
+    </row>
+    <row r="99">
+      <c r="E99" s="10" t="n"/>
+    </row>
+    <row r="100">
+      <c r="E100" s="10" t="n"/>
+    </row>
+    <row r="101">
+      <c r="E101" s="10" t="n"/>
+    </row>
+    <row r="102">
+      <c r="E102" s="10" t="n"/>
+    </row>
+    <row r="103">
+      <c r="E103" s="10" t="n"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="10" t="n"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="10" t="n"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="10" t="n"/>
+    </row>
+    <row r="107">
+      <c r="E107" s="10" t="n"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="10" t="n"/>
+    </row>
+    <row r="109">
+      <c r="E109" s="10" t="n"/>
+    </row>
+    <row r="110">
+      <c r="E110" s="10" t="n"/>
+    </row>
+    <row r="111">
+      <c r="E111" s="10" t="n"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="10" t="n"/>
+    </row>
+    <row r="113">
+      <c r="E113" s="10" t="n"/>
+    </row>
+    <row r="114">
+      <c r="E114" s="10" t="n"/>
+    </row>
+    <row r="115">
+      <c r="E115" s="10" t="n"/>
+    </row>
+    <row r="116">
+      <c r="E116" s="10" t="n"/>
+    </row>
+    <row r="117">
+      <c r="E117" s="10" t="n"/>
+    </row>
+    <row r="118">
+      <c r="E118" s="10" t="n"/>
+    </row>
+    <row r="119">
+      <c r="E119" s="10" t="n"/>
+    </row>
+    <row r="120">
+      <c r="E120" s="10" t="n"/>
+    </row>
+    <row r="121">
+      <c r="E121" s="10" t="n"/>
+    </row>
+    <row r="122">
+      <c r="E122" s="10" t="n"/>
+    </row>
+    <row r="123">
+      <c r="E123" s="10" t="n"/>
+    </row>
+    <row r="124">
+      <c r="E124" s="10" t="n"/>
+    </row>
+    <row r="125">
+      <c r="E125" s="10" t="n"/>
+    </row>
+    <row r="126">
+      <c r="E126" s="10" t="n"/>
+    </row>
+    <row r="127">
+      <c r="E127" s="10" t="n"/>
+    </row>
+    <row r="128">
+      <c r="E128" s="10" t="n"/>
+    </row>
+    <row r="129">
+      <c r="E129" s="10" t="n"/>
+    </row>
+    <row r="130">
+      <c r="E130" s="10" t="n"/>
+    </row>
+    <row r="131">
+      <c r="E131" s="10" t="n"/>
+    </row>
+    <row r="132">
+      <c r="E132" s="10" t="n"/>
+    </row>
+    <row r="133">
+      <c r="E133" s="10" t="n"/>
+    </row>
+    <row r="134">
+      <c r="E134" s="10" t="n"/>
+    </row>
+    <row r="135">
+      <c r="E135" s="10" t="n"/>
+    </row>
+    <row r="136">
+      <c r="E136" s="10" t="n"/>
+    </row>
+    <row r="137">
+      <c r="E137" s="10" t="n"/>
+    </row>
+    <row r="138">
+      <c r="E138" s="10" t="n"/>
+    </row>
+    <row r="139">
+      <c r="E139" s="10" t="n"/>
+    </row>
+    <row r="140">
+      <c r="E140" s="10" t="n"/>
+    </row>
+    <row r="141">
+      <c r="E141" s="10" t="n"/>
+    </row>
+    <row r="142">
+      <c r="E142" s="10" t="n"/>
+    </row>
+    <row r="143">
+      <c r="E143" s="10" t="n"/>
+    </row>
+    <row r="144">
+      <c r="E144" s="10" t="n"/>
+    </row>
+    <row r="145">
+      <c r="E145" s="10" t="n"/>
+    </row>
+    <row r="146">
+      <c r="E146" s="10" t="n"/>
+    </row>
+    <row r="147">
+      <c r="E147" s="10" t="n"/>
+    </row>
+    <row r="148">
+      <c r="E148" s="10" t="n"/>
+    </row>
+    <row r="149">
+      <c r="E149" s="10" t="n"/>
+    </row>
+    <row r="150">
+      <c r="E150" s="10" t="n"/>
+    </row>
+    <row r="151">
+      <c r="E151" s="10" t="n"/>
+    </row>
+    <row r="152">
+      <c r="E152" s="10" t="n"/>
+    </row>
+    <row r="153">
+      <c r="E153" s="10" t="n"/>
+    </row>
+    <row r="154">
+      <c r="E154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="E155" s="10" t="n"/>
+    </row>
+    <row r="156">
+      <c r="E156" s="10" t="n"/>
+    </row>
+    <row r="157">
+      <c r="E157" s="10" t="n"/>
+    </row>
+    <row r="158">
+      <c r="E158" s="10" t="n"/>
+    </row>
+    <row r="159">
+      <c r="E159" s="10" t="n"/>
+    </row>
+    <row r="160">
+      <c r="E160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="E161" s="10" t="n"/>
+    </row>
+    <row r="162">
+      <c r="E162" s="10" t="n"/>
+    </row>
+    <row r="163">
+      <c r="E163" s="10" t="n"/>
+    </row>
+    <row r="164">
+      <c r="E164" s="10" t="n"/>
+    </row>
+    <row r="165">
+      <c r="E165" s="10" t="n"/>
+    </row>
+    <row r="166">
+      <c r="E166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="E167" s="10" t="n"/>
+    </row>
+    <row r="168">
+      <c r="E168" s="10" t="n"/>
+    </row>
+    <row r="169">
+      <c r="E169" s="10" t="n"/>
+    </row>
+    <row r="170">
+      <c r="E170" s="10" t="n"/>
+    </row>
+    <row r="171">
+      <c r="E171" s="10" t="n"/>
+    </row>
+    <row r="172">
+      <c r="E172" s="10" t="n"/>
+    </row>
+    <row r="173">
+      <c r="E173" s="10" t="n"/>
+    </row>
+    <row r="174">
+      <c r="E174" s="10" t="n"/>
+    </row>
+    <row r="175">
+      <c r="E175" s="10" t="n"/>
+    </row>
+    <row r="176">
+      <c r="E176" s="10" t="n"/>
+    </row>
+    <row r="177">
+      <c r="E177" s="10" t="n"/>
+    </row>
+    <row r="178">
+      <c r="E178" s="10" t="n"/>
+    </row>
+    <row r="179">
+      <c r="E179" s="10" t="n"/>
+    </row>
+    <row r="180">
+      <c r="E180" s="10" t="n"/>
+    </row>
+    <row r="181">
+      <c r="E181" s="10" t="n"/>
+    </row>
+    <row r="182">
+      <c r="E182" s="10" t="n"/>
+    </row>
+    <row r="183">
+      <c r="E183" s="10" t="n"/>
+    </row>
+    <row r="184">
+      <c r="E184" s="10" t="n"/>
+    </row>
+    <row r="185">
+      <c r="E185" s="10" t="n"/>
+    </row>
+    <row r="186">
+      <c r="E186" s="10" t="n"/>
+    </row>
+    <row r="187">
+      <c r="E187" s="10" t="n"/>
+    </row>
+    <row r="188">
+      <c r="E188" s="10" t="n"/>
+    </row>
+    <row r="189">
+      <c r="E189" s="10" t="n"/>
+    </row>
+    <row r="190">
+      <c r="E190" s="10" t="n"/>
+    </row>
+    <row r="191">
+      <c r="E191" s="10" t="n"/>
+    </row>
+    <row r="192">
+      <c r="E192" s="10" t="n"/>
+    </row>
+    <row r="193">
+      <c r="E193" s="10" t="n"/>
+    </row>
+    <row r="194">
+      <c r="E194" s="10" t="n"/>
+    </row>
+    <row r="195">
+      <c r="E195" s="10" t="n"/>
+    </row>
+    <row r="196">
+      <c r="E196" s="10" t="n"/>
+    </row>
+    <row r="197">
+      <c r="E197" s="10" t="n"/>
+    </row>
+    <row r="198">
+      <c r="E198" s="10" t="n"/>
+    </row>
+    <row r="199">
+      <c r="E199" s="10" t="n"/>
+    </row>
+    <row r="200">
+      <c r="E200" s="10" t="n"/>
+    </row>
+    <row r="201">
+      <c r="E201" s="10" t="n"/>
+    </row>
+    <row r="202">
+      <c r="E202" s="10" t="n"/>
+    </row>
+    <row r="203">
+      <c r="E203" s="10" t="n"/>
+    </row>
+    <row r="204">
+      <c r="E204" s="10" t="n"/>
+    </row>
+    <row r="205">
+      <c r="E205" s="10" t="n"/>
+    </row>
+    <row r="206">
+      <c r="E206" s="10" t="n"/>
+    </row>
+    <row r="207">
+      <c r="E207" s="10" t="n"/>
+    </row>
+    <row r="208">
+      <c r="E208" s="10" t="n"/>
+    </row>
+    <row r="209">
+      <c r="E209" s="10" t="n"/>
+    </row>
+    <row r="210">
+      <c r="E210" s="10" t="n"/>
+    </row>
+    <row r="211">
+      <c r="E211" s="10" t="n"/>
+    </row>
+    <row r="212">
+      <c r="E212" s="10" t="n"/>
+    </row>
+    <row r="213">
+      <c r="E213" s="10" t="n"/>
+    </row>
+    <row r="214">
+      <c r="E214" s="10" t="n"/>
+    </row>
+    <row r="215">
+      <c r="E215" s="10" t="n"/>
+    </row>
+    <row r="216">
+      <c r="E216" s="10" t="n"/>
+    </row>
+    <row r="217">
+      <c r="E217" s="10" t="n"/>
+    </row>
+    <row r="218">
+      <c r="E218" s="10" t="n"/>
+    </row>
+    <row r="219">
+      <c r="E219" s="10" t="n"/>
+    </row>
+    <row r="220">
+      <c r="E220" s="10" t="n"/>
+    </row>
+    <row r="221">
+      <c r="E221" s="10" t="n"/>
+    </row>
+    <row r="222">
+      <c r="E222" s="10" t="n"/>
+    </row>
+    <row r="223">
+      <c r="E223" s="10" t="n"/>
+    </row>
+    <row r="224">
+      <c r="E224" s="10" t="n"/>
+    </row>
+    <row r="225">
+      <c r="E225" s="10" t="n"/>
+    </row>
+    <row r="226">
+      <c r="E226" s="10" t="n"/>
+    </row>
+    <row r="227">
+      <c r="E227" s="10" t="n"/>
+    </row>
+    <row r="228">
+      <c r="E228" s="10" t="n"/>
+    </row>
+    <row r="229">
+      <c r="E229" s="10" t="n"/>
+    </row>
+    <row r="230">
+      <c r="E230" s="10" t="n"/>
+    </row>
+    <row r="231">
+      <c r="E231" s="10" t="n"/>
+    </row>
+    <row r="232">
+      <c r="E232" s="10" t="n"/>
+    </row>
+    <row r="233">
+      <c r="E233" s="10" t="n"/>
+    </row>
+    <row r="234">
+      <c r="E234" s="10" t="n"/>
+    </row>
+    <row r="235">
+      <c r="E235" s="10" t="n"/>
+    </row>
+    <row r="236">
+      <c r="E236" s="10" t="n"/>
+    </row>
+    <row r="237">
+      <c r="E237" s="10" t="n"/>
+    </row>
+    <row r="238">
+      <c r="E238" s="10" t="n"/>
+    </row>
+    <row r="239">
+      <c r="E239" s="10" t="n"/>
+    </row>
+    <row r="240">
+      <c r="E240" s="10" t="n"/>
+    </row>
+    <row r="241">
+      <c r="E241" s="10" t="n"/>
+    </row>
+    <row r="242">
+      <c r="E242" s="10" t="n"/>
+    </row>
+    <row r="243">
+      <c r="E243" s="10" t="n"/>
+    </row>
+    <row r="244">
+      <c r="E244" s="10" t="n"/>
+    </row>
+    <row r="245">
+      <c r="E245" s="10" t="n"/>
+    </row>
+    <row r="246">
+      <c r="E246" s="10" t="n"/>
+    </row>
+    <row r="247">
+      <c r="E247" s="10" t="n"/>
+    </row>
+    <row r="248">
+      <c r="E248" s="10" t="n"/>
+    </row>
+    <row r="249">
+      <c r="E249" s="10" t="n"/>
+    </row>
+    <row r="250">
+      <c r="E250" s="10" t="n"/>
+    </row>
+    <row r="251">
+      <c r="E251" s="10" t="n"/>
+    </row>
+    <row r="252">
+      <c r="E252" s="10" t="n"/>
+    </row>
+    <row r="253">
+      <c r="E253" s="10" t="n"/>
+    </row>
+    <row r="254">
+      <c r="E254" s="10" t="n"/>
+    </row>
+    <row r="255">
+      <c r="E255" s="10" t="n"/>
+    </row>
+    <row r="256">
+      <c r="E256" s="10" t="n"/>
+    </row>
+    <row r="257">
+      <c r="E257" s="10" t="n"/>
+    </row>
+    <row r="258">
+      <c r="E258" s="10" t="n"/>
+    </row>
+    <row r="259">
+      <c r="E259" s="10" t="n"/>
+    </row>
+    <row r="260">
+      <c r="E260" s="10" t="n"/>
+    </row>
+    <row r="261">
+      <c r="E261" s="10" t="n"/>
+    </row>
+    <row r="262">
+      <c r="E262" s="10" t="n"/>
+    </row>
+    <row r="263">
+      <c r="E263" s="10" t="n"/>
+    </row>
+    <row r="264">
+      <c r="E264" s="10" t="n"/>
+    </row>
+    <row r="265">
+      <c r="E265" s="10" t="n"/>
+    </row>
+    <row r="266">
+      <c r="E266" s="10" t="n"/>
+    </row>
+    <row r="267">
+      <c r="E267" s="10" t="n"/>
+    </row>
+    <row r="268">
+      <c r="E268" s="10" t="n"/>
+    </row>
+    <row r="269">
+      <c r="E269" s="10" t="n"/>
+    </row>
+    <row r="270">
+      <c r="E270" s="10" t="n"/>
+    </row>
+    <row r="271">
+      <c r="E271" s="10" t="n"/>
+    </row>
+    <row r="272">
+      <c r="E272" s="10" t="n"/>
+    </row>
+    <row r="273">
+      <c r="E273" s="10" t="n"/>
+    </row>
+    <row r="274">
+      <c r="E274" s="10" t="n"/>
+    </row>
+    <row r="275">
+      <c r="E275" s="10" t="n"/>
+    </row>
+    <row r="276">
+      <c r="E276" s="10" t="n"/>
+    </row>
+    <row r="277">
+      <c r="E277" s="10" t="n"/>
+    </row>
+    <row r="278">
+      <c r="E278" s="10" t="n"/>
+    </row>
+    <row r="279">
+      <c r="E279" s="10" t="n"/>
+    </row>
+    <row r="280">
+      <c r="E280" s="10" t="n"/>
+    </row>
+    <row r="281">
+      <c r="E281" s="10" t="n"/>
+    </row>
+    <row r="282">
+      <c r="E282" s="10" t="n"/>
+    </row>
+    <row r="283">
+      <c r="E283" s="10" t="n"/>
+    </row>
+    <row r="284">
+      <c r="E284" s="10" t="n"/>
+    </row>
+    <row r="285">
+      <c r="E285" s="10" t="n"/>
+    </row>
+    <row r="286">
+      <c r="E286" s="10" t="n"/>
+    </row>
+    <row r="287">
+      <c r="E287" s="10" t="n"/>
+    </row>
+    <row r="288">
+      <c r="E288" s="10" t="n"/>
+    </row>
+    <row r="289">
+      <c r="E289" s="10" t="n"/>
+    </row>
+    <row r="290">
+      <c r="E290" s="10" t="n"/>
+    </row>
+    <row r="291">
+      <c r="E291" s="10" t="n"/>
+    </row>
+    <row r="292">
+      <c r="E292" s="10" t="n"/>
+    </row>
+    <row r="293">
+      <c r="E293" s="10" t="n"/>
+    </row>
+    <row r="294">
+      <c r="E294" s="10" t="n"/>
+    </row>
+    <row r="295">
+      <c r="E295" s="10" t="n"/>
+    </row>
+    <row r="296">
+      <c r="E296" s="10" t="n"/>
+    </row>
+    <row r="297">
+      <c r="E297" s="10" t="n"/>
+    </row>
+    <row r="298">
+      <c r="E298" s="10" t="n"/>
+    </row>
+    <row r="299">
+      <c r="E299" s="10" t="n"/>
+    </row>
+    <row r="300">
+      <c r="E300" s="10" t="n"/>
+    </row>
+    <row r="301">
+      <c r="E301" s="10" t="n"/>
+    </row>
+    <row r="302">
+      <c r="E302" s="10" t="n"/>
+    </row>
+    <row r="303">
+      <c r="E303" s="10" t="n"/>
+    </row>
+    <row r="304">
+      <c r="E304" s="10" t="n"/>
+    </row>
+    <row r="305">
+      <c r="E305" s="10" t="n"/>
+    </row>
+    <row r="306">
+      <c r="E306" s="10" t="n"/>
+    </row>
+    <row r="307">
+      <c r="E307" s="10" t="n"/>
+    </row>
+    <row r="308">
+      <c r="E308" s="10" t="n"/>
+    </row>
+    <row r="309">
+      <c r="E309" s="10" t="n"/>
+    </row>
+    <row r="310">
+      <c r="E310" s="10" t="n"/>
+    </row>
+    <row r="311">
+      <c r="E311" s="10" t="n"/>
+    </row>
+    <row r="312">
+      <c r="E312" s="10" t="n"/>
+    </row>
+    <row r="313">
+      <c r="E313" s="10" t="n"/>
+    </row>
+    <row r="314">
+      <c r="E314" s="10" t="n"/>
+    </row>
+    <row r="315">
+      <c r="E315" s="10" t="n"/>
+    </row>
+    <row r="316">
+      <c r="E316" s="10" t="n"/>
+    </row>
+    <row r="317">
+      <c r="E317" s="10" t="n"/>
+    </row>
+    <row r="318">
+      <c r="E318" s="10" t="n"/>
+    </row>
+    <row r="319">
+      <c r="E319" s="10" t="n"/>
+    </row>
+    <row r="320">
+      <c r="E320" s="10" t="n"/>
+    </row>
+    <row r="321">
+      <c r="E321" s="10" t="n"/>
+    </row>
+    <row r="322">
+      <c r="E322" s="10" t="n"/>
+    </row>
+    <row r="323">
+      <c r="E323" s="10" t="n"/>
+    </row>
+    <row r="324">
+      <c r="E324" s="10" t="n"/>
+    </row>
+    <row r="325">
+      <c r="E325" s="10" t="n"/>
+    </row>
+    <row r="326">
+      <c r="E326" s="10" t="n"/>
+    </row>
+    <row r="327">
+      <c r="E327" s="10" t="n"/>
+    </row>
+    <row r="328">
+      <c r="E328" s="10" t="n"/>
+    </row>
+    <row r="329">
+      <c r="E329" s="10" t="n"/>
+    </row>
+    <row r="330">
+      <c r="E330" s="10" t="n"/>
+    </row>
+    <row r="331">
+      <c r="E331" s="10" t="n"/>
+    </row>
+    <row r="332">
+      <c r="E332" s="10" t="n"/>
+    </row>
+    <row r="333">
+      <c r="E333" s="10" t="n"/>
+    </row>
+    <row r="334">
+      <c r="E334" s="10" t="n"/>
+    </row>
+    <row r="335">
+      <c r="E335" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:E335"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="15" customWidth="1" style="4" min="1" max="1"/>
+    <col width="12" customWidth="1" style="4" min="2" max="2"/>
+    <col width="17.5" customWidth="1" style="4" min="3" max="3"/>
+    <col width="15.75" customWidth="1" style="4" min="4" max="4"/>
+    <col width="21.625" customWidth="1" style="4" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>드롭 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>아이템 TID</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>확률가중치</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>설명 (메모 — 로직 미사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ItemTable.ItemTID</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>DropTID</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ItemTID</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>501</v>
+      </c>
+      <c r="C10" t="n">
+        <v>50001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6590</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>질긴 고기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>502</v>
+      </c>
+      <c r="C11" t="n">
+        <v>50002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>토끼 가죽</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>503</v>
+      </c>
+      <c r="C12" t="n">
+        <v>50003</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>늑대 가죽</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>504</v>
+      </c>
+      <c r="C13" t="n">
+        <v>50004</v>
+      </c>
+      <c r="D13" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>곰 모피</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>505</v>
+      </c>
+      <c r="C14" t="n">
+        <v>50005</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>거대한 뿔</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>506</v>
+      </c>
+      <c r="C15" t="n">
+        <v>50006</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>마수의 심장</t>
+        </is>
       </c>
     </row>
     <row r="16">
